--- a/Trục đường/Du_lieu_nut_thap_diem.xlsx
+++ b/Trục đường/Du_lieu_nut_thap_diem.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6690"/>
   </bookViews>
   <sheets>
-    <sheet name="Baseline_10Nut_ThapDiem_Dep" sheetId="1" r:id="rId1"/>
+    <sheet name="thap_diem" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
